--- a/output/01_共通_基本コラム部品.xlsx
+++ b/output/01_共通_基本コラム部品.xlsx
@@ -8,16 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="表紙・凡例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="差込データ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="共通項目定義" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="部品マスタ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="レイアウト一覧" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="デザインルール" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="使い分けガイド" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="部品画像一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="差込データ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="共通項目定義" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="部品マスタ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="レイアウト一覧" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="デザインルール" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="使い分けガイド" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'差込データ'!$A$1:$L$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'部品マスタ'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'差込データ'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'部品マスタ'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +63,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="12">
@@ -122,7 +128,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -144,11 +150,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -191,6 +241,14 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -266,6 +324,161 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3343275" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3343275" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3343275" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3343275" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3343275" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3343275" cy="2057400"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -650,8 +863,8 @@
           <t>Wordへ差し込むデータ本体（1行=1コラム）</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="18" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -664,8 +877,8 @@
           <t>差込フィールドの一覧と必須／任意区分</t>
         </is>
       </c>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="18" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -678,8 +891,8 @@
           <t>部品の用途・使用例・推奨レイアウト一覧</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="18" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -692,8 +905,8 @@
           <t>6パターンのレイアウトと使い分け</t>
         </is>
       </c>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="18" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -706,8 +919,8 @@
           <t>配色・余白・フォントの統一ルール</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="18" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -720,8 +933,8 @@
           <t>部品名／主な用途／使用頻度（★）</t>
         </is>
       </c>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="18" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -844,8 +1057,8 @@
   <mergeCells count="9">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:D15"/>
@@ -857,6 +1070,203 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>基本コラム部品（共通）　画像見本一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>部品ID</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>部品名</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>画像見本</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>主な用途</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>使用例</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="180" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>BC-01</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>ポイント</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>計画の要点や重要なポイントを簡潔にまとめる欄です。</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>基本方針、重点事項、留意点 等</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="180" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>BC-02</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>コラム</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>本文の補足説明や背景情報、豆知識などを掲載する欄です。</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>制度説明、背景解説、考え方 等</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="180" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>BC-03</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>事例紹介</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>地域や他自治体の取り組み事例を紹介する欄です。</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>活動事例、先進事例、参考事例 等</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="180" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>BC-04</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>解説</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>制度や用語の解説、専門的内容をわかりやすく説明する欄です。</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>制度解説、用語解説、法令解説 等</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="180" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>BC-05</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>データの見方</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>図表・グラフの読み方や注意点を説明する補足です。</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>図表の補足、数値の見方 等</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="180" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>BC-06</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>注意・留意点</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>計画推進にあたり注意すべき事項や留意点を示す欄です。</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>留意事項、リスク、注意喚起 等</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1295,7 +1705,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1545,7 +1955,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1864,7 +2274,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2012,7 +2422,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2045,6 +2455,7 @@
           <t>✓ アイコンは同じ線幅・同じスタイルで統一</t>
         </is>
       </c>
+      <c r="B4" s="18" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -2052,6 +2463,7 @@
           <t>✓ 余白（内側8〜12mm程度）を確保して読みやすく</t>
         </is>
       </c>
+      <c r="B5" s="18" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2059,6 +2471,7 @@
           <t>✓ 色は淡いトーンで、本文より主張させない</t>
         </is>
       </c>
+      <c r="B6" s="18" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -2066,6 +2479,7 @@
           <t>✓ 1ページにコラムは最大2個程度が基本</t>
         </is>
       </c>
+      <c r="B7" s="18" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -2073,6 +2487,7 @@
           <t>✓ フォントは本文と同じ（游ゴシック等）を使用</t>
         </is>
       </c>
+      <c r="B8" s="18" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -2080,6 +2495,7 @@
           <t>✓ 印刷したときに見やすい濃さで設計</t>
         </is>
       </c>
+      <c r="B9" s="18" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2176,7 +2592,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/output/01_共通_基本コラム部品.xlsx
+++ b/output/01_共通_基本コラム部品.xlsx
@@ -1,24 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="表紙・凡例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="部品画像一覧" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="差込データ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="共通項目定義" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="部品マスタ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="レイアウト一覧" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="デザインルール" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="使い分けガイド" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表紙・凡例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="差込データ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="共通項目定義" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部品マスタ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="レイアウト一覧" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="デザインルール" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い分けガイド" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'差込データ'!$A$1:$L$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'部品マスタ'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'差込データ'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'部品マスタ'!$A$1:$H$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -29,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,11 +62,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="游ゴシック"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="12">
@@ -128,7 +122,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -150,55 +144,11 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -241,14 +191,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -324,161 +266,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>3</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3343275" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3343275" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3343275" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3343275" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3343275" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3343275" cy="2057400"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -863,8 +650,8 @@
           <t>Wordへ差し込むデータ本体（1行=1コラム）</t>
         </is>
       </c>
-      <c r="C10" s="17" t="n"/>
-      <c r="D10" s="18" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -877,8 +664,8 @@
           <t>差込フィールドの一覧と必須／任意区分</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="18" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -891,8 +678,8 @@
           <t>部品の用途・使用例・推奨レイアウト一覧</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="18" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -905,8 +692,8 @@
           <t>6パターンのレイアウトと使い分け</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n"/>
-      <c r="D13" s="18" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -919,8 +706,8 @@
           <t>配色・余白・フォントの統一ルール</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="18" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -933,8 +720,8 @@
           <t>部品名／主な用途／使用頻度（★）</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="18" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1057,8 +844,8 @@
   <mergeCells count="9">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="B11:D11"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B15:D15"/>
@@ -1070,203 +857,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="78" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>基本コラム部品（共通）　画像見本一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>部品ID</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>部品名</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>画像見本</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>主な用途</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>使用例</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="180" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>BC-01</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>ポイント</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr"/>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>計画の要点や重要なポイントを簡潔にまとめる欄です。</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>基本方針、重点事項、留意点 等</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="180" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>BC-02</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>コラム</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>本文の補足説明や背景情報、豆知識などを掲載する欄です。</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>制度説明、背景解説、考え方 等</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="180" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>BC-03</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>事例紹介</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>地域や他自治体の取り組み事例を紹介する欄です。</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>活動事例、先進事例、参考事例 等</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="180" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>BC-04</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>解説</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr"/>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>制度や用語の解説、専門的内容をわかりやすく説明する欄です。</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>制度解説、用語解説、法令解説 等</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="180" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>BC-05</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>データの見方</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>図表・グラフの読み方や注意点を説明する補足です。</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>図表の補足、数値の見方 等</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="180" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>BC-06</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>注意・留意点</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr"/>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>計画推進にあたり注意すべき事項や留意点を示す欄です。</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>留意事項、リスク、注意喚起 等</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1705,7 +1295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1955,7 +1545,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2274,7 +1864,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2422,7 +2012,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2455,7 +2045,6 @@
           <t>✓ アイコンは同じ線幅・同じスタイルで統一</t>
         </is>
       </c>
-      <c r="B4" s="18" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -2463,7 +2052,6 @@
           <t>✓ 余白（内側8〜12mm程度）を確保して読みやすく</t>
         </is>
       </c>
-      <c r="B5" s="18" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2471,7 +2059,6 @@
           <t>✓ 色は淡いトーンで、本文より主張させない</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -2479,7 +2066,6 @@
           <t>✓ 1ページにコラムは最大2個程度が基本</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -2487,7 +2073,6 @@
           <t>✓ フォントは本文と同じ（游ゴシック等）を使用</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -2495,7 +2080,6 @@
           <t>✓ 印刷したときに見やすい濃さで設計</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -2592,7 +2176,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/output/01_共通_基本コラム部品.xlsx
+++ b/output/01_共通_基本コラム部品.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>部品名／主な用途／使用頻度（★）</t>
+          <t>部品名／主な用途／使用頻度（）</t>
         </is>
       </c>
       <c r="C15" s="8" t="n"/>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>★1〜5</t>
+          <t>1〜5</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
